--- a/docs/files/2026-10-22/상담행정공고_2026-10-22.xlsx
+++ b/docs/files/2026-10-22/상담행정공고_2026-10-22.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -588,28 +588,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 교육</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>학교밖청소년 대안교육기관 내일더하기</t>
+          <t>정립회관</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>학교밖청소년 대안교육기관 내일더하기 상근교사 채용공고</t>
+          <t>정립회관 육아휴직 대체 인력 채용 공고(장애인재활상담사/사회복지사)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>계약직 · 대체인력</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 중랑구</t>
+          <t>서울특별시 광진구</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -620,17 +620,17 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -642,29 +642,25 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072962</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071979</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>청소년 · 교육</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>중랑구청소년커뮤니티공간딩가동4번지</t>
+          <t>학교밖청소년 대안교육기관 내일더하기</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>중랑구청소년커뮤니티공간딩가동4번지 청소년지도사 채용공고</t>
+          <t>학교밖청소년 대안교육기관 내일더하기 상근교사 채용공고</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -685,17 +681,17 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -707,14 +703,14 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072961</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072962</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -724,22 +720,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>중랑구청소년커뮤니티공간딩가동4번지</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+          <t>중랑구청소년커뮤니티공간딩가동4번지 청소년지도사 채용공고</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
+          <t>서울특별시 중랑구</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -750,17 +746,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -772,31 +768,39 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072961</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr"/>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>아담스지역아동센터</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>서울특별시 노원구</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -807,17 +811,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-32</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -829,56 +833,56 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>마음드림심리상담센터 광명점</t>
+          <t>새터민청소년그룹홈 가족</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
+          <t>새터민청소년그룹홈 &lt;가족&gt; 보육팀 사회복지사 모집</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>경기도 광명시</t>
+          <t>서울특별시 성북구</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -890,56 +894,52 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074658</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
+          <t>아담스지역아동센터</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>경기도 용인시</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-32</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -951,25 +951,25 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관</t>
+          <t>마음드림심리상담센터 광명점</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
+          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -979,28 +979,28 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>경기도 광명시</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1012,25 +1012,25 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
+          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
+          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1040,28 +1040,28 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
+          <t>경기도 용인시</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1073,35 +1073,35 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동)</t>
+          <t>시흥장애인종합복지관</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
+          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>파트타임</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1112,17 +1112,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1134,35 +1134,35 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 교육</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>안산시글로벌청소년센터</t>
+          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>[안산시글로벌청소년센터] 교육진로팀 팀원 채용 공고</t>
+          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시</t>
+          <t>경기도 안양시</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1173,17 +1173,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-4</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
@@ -1195,35 +1195,35 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073853</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>경기해바라기센터(아동)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
+          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>시간제</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 단원구</t>
+          <t>경기도 성남시 분당구</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1256,31 +1256,35 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 교육</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>안산시장애인복지관</t>
+          <t>안산시글로벌청소년센터</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>[안산시글로벌청소년센터] 교육진로팀 팀원 채용 공고</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 안산시</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1291,7 +1295,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1313,25 +1317,25 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073853</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>빅사랑</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
+          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1341,7 +1345,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>경기도 안산시 상록구</t>
+          <t>경기도 안산시 단원구</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -1357,12 +1361,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-9</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1374,25 +1378,25 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>수원희망의집</t>
+          <t>안산시장애인복지관</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
+          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1409,17 +1413,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-6</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1431,35 +1435,35 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>아담중증장애인거주시설</t>
+          <t>빅사랑</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 유성구</t>
+          <t>경기도 안산시 상록구</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1475,12 +1479,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1492,25 +1496,25 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>여성인권지원상담소 '느티나무'</t>
+          <t>주식회사온무지개</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
+          <t>주식회사온무지개 주간(성인)활동서비스 및 청소년발달장애인 방과후활동서비스사업 [사회복지사]</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1520,28 +1524,28 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 중구</t>
+          <t>경기도 김포시</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-9</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -1553,52 +1557,56 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1074565</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>여성인권지원상담소'느티나무'</t>
+          <t>수원희망의집</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>아동청소년 그룹홈 생활보육사 1명 채용공고</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>대전광역시</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-6</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
@@ -1610,12 +1618,252 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073939</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>시흥시남자단기청소년쉼터</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>D-12</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>아담중증장애인거주시설</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 유성구</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>여성인권지원상담소 '느티나무'</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>D-6</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>여성인권지원상담소'느티나무'</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>D-6</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073488</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
+  <autoFilter ref="A1:O23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
